--- a/稳健组类型.xlsx
+++ b/稳健组类型.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liy22223\Desktop\FCN筛选器v1\screener\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liy22223\Desktop\FCN_老板候选池v8_转换\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B3BA89-EA55-4BAC-BCC8-652D61B1F062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66991308-4C7B-4036-AAF2-C9DAB160BC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="69">
   <si>
     <t>区域</t>
   </si>
@@ -52,172 +52,181 @@
     <t>美股</t>
   </si>
   <si>
-    <t>LRCX US</t>
-  </si>
-  <si>
-    <t>泛林集团</t>
-  </si>
-  <si>
-    <t>半导体设备与材料</t>
+    <t>NXPI US</t>
+  </si>
+  <si>
+    <t>恩智浦</t>
+  </si>
+  <si>
+    <t>半导体</t>
   </si>
   <si>
     <t>欧式敲入</t>
   </si>
   <si>
-    <t>AMD US</t>
-  </si>
-  <si>
-    <t>美国超微公司</t>
-  </si>
-  <si>
-    <t>半导体</t>
+    <t>GEV US</t>
+  </si>
+  <si>
+    <t>GE Vernova</t>
+  </si>
+  <si>
+    <t>电力设备</t>
+  </si>
+  <si>
+    <t>ANET US</t>
+  </si>
+  <si>
+    <t>Arista</t>
+  </si>
+  <si>
+    <t>AI 网络</t>
   </si>
   <si>
     <t>ASML US</t>
   </si>
   <si>
-    <t>阿斯麦</t>
-  </si>
-  <si>
-    <t>AMAT US</t>
-  </si>
-  <si>
-    <t>应用材料</t>
-  </si>
-  <si>
-    <t>DELL US</t>
-  </si>
-  <si>
-    <t>戴尔科技</t>
-  </si>
-  <si>
-    <t>计算机硬件</t>
-  </si>
-  <si>
-    <t>KLAC US</t>
-  </si>
-  <si>
-    <t>科磊</t>
-  </si>
-  <si>
-    <t>FLEX US</t>
-  </si>
-  <si>
-    <t>伟创力</t>
-  </si>
-  <si>
-    <t>电子元件</t>
-  </si>
-  <si>
-    <t>GLW US</t>
-  </si>
-  <si>
-    <t>康宁</t>
+    <t>ASML</t>
+  </si>
+  <si>
+    <t>半导体设备</t>
+  </si>
+  <si>
+    <t>SNOW US</t>
+  </si>
+  <si>
+    <t>Snowflake</t>
+  </si>
+  <si>
+    <t>数据云</t>
+  </si>
+  <si>
+    <t>AVGO US</t>
+  </si>
+  <si>
+    <t>Broadcom</t>
+  </si>
+  <si>
+    <t>CRWD US</t>
+  </si>
+  <si>
+    <t>CrowdStrike</t>
+  </si>
+  <si>
+    <t>网络安全</t>
+  </si>
+  <si>
+    <t>NVDA US</t>
+  </si>
+  <si>
+    <t>NVIDIA</t>
+  </si>
+  <si>
+    <t>AI 芯片</t>
+  </si>
+  <si>
+    <t>ABNB US</t>
+  </si>
+  <si>
+    <t>Airbnb</t>
+  </si>
+  <si>
+    <t>旅游</t>
+  </si>
+  <si>
+    <t>ORCL US</t>
+  </si>
+  <si>
+    <t>甲骨文</t>
+  </si>
+  <si>
+    <t>云/AI</t>
   </si>
   <si>
     <t>PANW US</t>
   </si>
   <si>
-    <t>Palo Alto Networks</t>
-  </si>
-  <si>
-    <t>软件基础设施</t>
-  </si>
-  <si>
-    <t>CSCO US</t>
-  </si>
-  <si>
-    <t>思科</t>
-  </si>
-  <si>
-    <t>通讯设备</t>
-  </si>
-  <si>
-    <t>TSM US</t>
-  </si>
-  <si>
-    <t>台积电</t>
-  </si>
-  <si>
-    <t>DDOG US</t>
-  </si>
-  <si>
-    <t>Datadog</t>
-  </si>
-  <si>
-    <t>应用软件</t>
-  </si>
-  <si>
-    <t>CAT US</t>
-  </si>
-  <si>
-    <t>卡特彼勒</t>
-  </si>
-  <si>
-    <t>农业和重型机械</t>
+    <t>Palo Alto</t>
+  </si>
+  <si>
+    <t>ABBV US</t>
+  </si>
+  <si>
+    <t>艾伯维</t>
+  </si>
+  <si>
+    <t>制药</t>
+  </si>
+  <si>
+    <t>MRK US</t>
+  </si>
+  <si>
+    <t>默克</t>
+  </si>
+  <si>
+    <t>GE US</t>
+  </si>
+  <si>
+    <t>GE 航空</t>
+  </si>
+  <si>
+    <t>航空</t>
   </si>
   <si>
     <t>港股</t>
   </si>
   <si>
-    <t>700 HK</t>
-  </si>
-  <si>
-    <t>腾讯控股</t>
-  </si>
-  <si>
-    <t>数码解决方案服务</t>
-  </si>
-  <si>
-    <t>981 HK</t>
-  </si>
-  <si>
-    <t>中芯国际</t>
-  </si>
-  <si>
-    <t>3750 HK</t>
-  </si>
-  <si>
-    <t>宁德时代</t>
-  </si>
-  <si>
-    <t>能源储存装置</t>
+    <t>1888 HK</t>
+  </si>
+  <si>
+    <t>蔚来</t>
+  </si>
+  <si>
+    <t>EV</t>
+  </si>
+  <si>
+    <t>2338 HK</t>
+  </si>
+  <si>
+    <t>潍柴动力</t>
+  </si>
+  <si>
+    <t>动力系统</t>
+  </si>
+  <si>
+    <t>9626 HK</t>
+  </si>
+  <si>
+    <t>哔哩哔哩</t>
+  </si>
+  <si>
+    <t>视频社区</t>
+  </si>
+  <si>
+    <t>3808 HK</t>
+  </si>
+  <si>
+    <t>中国重汽</t>
+  </si>
+  <si>
+    <t>商用车</t>
   </si>
   <si>
     <t>9988 HK</t>
   </si>
   <si>
-    <t>阿里巴巴-W</t>
-  </si>
-  <si>
-    <t>线上零售商</t>
-  </si>
-  <si>
-    <t>941 HK</t>
-  </si>
-  <si>
-    <t>中国移动</t>
-  </si>
-  <si>
-    <t>电讯服务</t>
-  </si>
-  <si>
-    <t>2899 HK</t>
-  </si>
-  <si>
-    <t>紫金矿业</t>
-  </si>
-  <si>
-    <t>黄金及贵金属</t>
-  </si>
-  <si>
-    <t>1211 HK</t>
-  </si>
-  <si>
-    <t>比亚迪股份</t>
-  </si>
-  <si>
-    <t>汽车</t>
+    <t>阿里巴巴</t>
+  </si>
+  <si>
+    <t>电商/云</t>
+  </si>
+  <si>
+    <t>1818 HK</t>
+  </si>
+  <si>
+    <t>招金矿业</t>
+  </si>
+  <si>
+    <t>黄金</t>
   </si>
 </sst>
 </file>
@@ -590,7 +599,7 @@
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
@@ -652,7 +661,7 @@
         <v>1.01</v>
       </c>
       <c r="I2" s="3">
-        <v>0.35089999999999999</v>
+        <v>0.20300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -681,7 +690,7 @@
         <v>1.01</v>
       </c>
       <c r="I3" s="3">
-        <v>0.32400000000000001</v>
+        <v>0.18179999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -695,7 +704,7 @@
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2">
         <v>0.8</v>
@@ -710,7 +719,7 @@
         <v>1.01</v>
       </c>
       <c r="I4" s="3">
-        <v>0.2117</v>
+        <v>0.2261</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -718,13 +727,13 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E5" s="2">
         <v>0.8</v>
@@ -739,7 +748,7 @@
         <v>1.01</v>
       </c>
       <c r="I5" s="3">
-        <v>0.32600000000000001</v>
+        <v>0.2021</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -747,13 +756,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2">
         <v>0.8</v>
@@ -768,7 +777,7 @@
         <v>1.01</v>
       </c>
       <c r="I6" s="3">
-        <v>0.36</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -776,10 +785,10 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
@@ -797,7 +806,7 @@
         <v>1.01</v>
       </c>
       <c r="I7" s="3">
-        <v>0.3417</v>
+        <v>0.1573</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -805,13 +814,13 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2">
         <v>0.8</v>
@@ -826,7 +835,7 @@
         <v>1.01</v>
       </c>
       <c r="I8" s="3">
-        <v>0.32750000000000001</v>
+        <v>0.1817</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -834,13 +843,13 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2">
         <v>0.8</v>
@@ -855,7 +864,7 @@
         <v>1.01</v>
       </c>
       <c r="I9" s="3">
-        <v>0.35320000000000001</v>
+        <v>0.1076</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -863,13 +872,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2">
         <v>0.8</v>
@@ -884,7 +893,7 @@
         <v>1.01</v>
       </c>
       <c r="I10" s="3">
-        <v>0.1714</v>
+        <v>8.0100000000000005E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -892,13 +901,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E11" s="2">
         <v>0.8</v>
@@ -913,7 +922,7 @@
         <v>1.01</v>
       </c>
       <c r="I11" s="3">
-        <v>0.12</v>
+        <v>0.21990000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -921,13 +930,13 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E12" s="2">
         <v>0.8</v>
@@ -942,7 +951,7 @@
         <v>1.01</v>
       </c>
       <c r="I12" s="3">
-        <v>0.17219999999999999</v>
+        <v>0.16120000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -950,13 +959,13 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E13" s="2">
         <v>0.8</v>
@@ -971,7 +980,7 @@
         <v>1.01</v>
       </c>
       <c r="I13" s="3">
-        <v>0.26729999999999998</v>
+        <v>3.6299999999999999E-2</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -979,10 +988,10 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
         <v>44</v>
@@ -1000,21 +1009,21 @@
         <v>1.01</v>
       </c>
       <c r="I14" s="3">
-        <v>0.1268</v>
+        <v>4.9599999999999998E-2</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E15" s="2">
         <v>0.8</v>
@@ -1029,21 +1038,21 @@
         <v>1.01</v>
       </c>
       <c r="I15" s="3">
-        <v>5.96E-2</v>
+        <v>7.6799999999999993E-2</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="E16" s="2">
         <v>0.8</v>
@@ -1058,21 +1067,21 @@
         <v>1.01</v>
       </c>
       <c r="I16" s="3">
-        <v>0.25069999999999998</v>
+        <v>0.38629999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E17" s="2">
         <v>0.8</v>
@@ -1087,21 +1096,21 @@
         <v>1.01</v>
       </c>
       <c r="I17" s="3">
-        <v>0.14410000000000001</v>
+        <v>0.1575</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E18" s="2">
         <v>0.8</v>
@@ -1116,21 +1125,21 @@
         <v>1.01</v>
       </c>
       <c r="I18" s="3">
-        <v>0.1105</v>
+        <v>0.18149999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E19" s="2">
         <v>0.8</v>
@@ -1145,21 +1154,21 @@
         <v>1.01</v>
       </c>
       <c r="I19" s="3">
-        <v>4.0000000000000001E-3</v>
+        <v>0.12089999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E20" s="2">
         <v>0.8</v>
@@ -1174,21 +1183,21 @@
         <v>1.01</v>
       </c>
       <c r="I20" s="3">
-        <v>0.153</v>
+        <v>0.1145</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E21" s="2">
         <v>0.8</v>
@@ -1203,7 +1212,7 @@
         <v>1.01</v>
       </c>
       <c r="I21" s="3">
-        <v>9.7900000000000001E-2</v>
+        <v>0.17799999999999999</v>
       </c>
     </row>
   </sheetData>
